--- a/survey_templates/017_swim_team_survey--survey_templates.xlsx
+++ b/survey_templates/017_swim_team_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1296,17 +1296,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>swim_distance_choices</t>
+          <t>swim_stroke_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1600m</t>
+          <t>front_crawl</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1600m</t>
+          <t>front crawl</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>front_crawl</t>
+          <t>backstroke</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>front crawl</t>
+          <t>backstroke</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>backstroke</t>
+          <t>breaststroke</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>backstroke</t>
+          <t>breaststroke</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>breaststroke</t>
+          <t>butterfly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>breaststroke</t>
+          <t>butterfly</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>freestyle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>butterfly</t>
+          <t>freestyle</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>swim_stroke_choices</t>
+          <t>swim_event_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>freestyle</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>freestyle</t>
+          <t>100m</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100m</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100m</t>
+          <t>200m</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>400m</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>400m</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>800m</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>800m</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>800m</t>
+          <t>1500m</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>800m</t>
+          <t>1500m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>swim_event_choices</t>
+          <t>swim_meet_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1500m</t>
+          <t>qualifying</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1500m</t>
+          <t>qualifying</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qualifying</t>
+          <t>invitational</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>qualifying</t>
+          <t>invitational</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>invitational</t>
+          <t>championship</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>invitational</t>
+          <t>championship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>swim_meet_choices</t>
+          <t>swim_meet_details_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>championship</t>
+          <t>warmup</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>championship</t>
+          <t>warmup</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>warmup</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warmup</t>
+          <t>heat</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>heat</t>
+          <t>final</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>heat</t>
+          <t>final</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>swim_meet_details_choices</t>
+          <t>swim_meet_result_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>won</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>won</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>lost</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>swim_meet_result_choices</t>
+          <t>swim_meet_rank_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>swim_meet_rank_choices</t>
+          <t>swim_meet_medal_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>gold</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>silver</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>bronze</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>bronze</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>swim_meet_medal_choices</t>
+          <t>swim_meet_ribbon_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bronze</t>
+          <t>ribbon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bronze</t>
+          <t>ribbon</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ribbon</t>
+          <t>no_ribbon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ribbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>swim_meet_ribbon_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>no_ribbon</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>no_ribbon</t>
+          <t>no ribbon</t>
         </is>
       </c>
     </row>
